--- a/3DAG and 2D Tree/Data Summaries/Uniform 100 x 100.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/Uniform 100 x 100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07A8172-0E73-4E42-A75F-2B6806FAB8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CAB9C3-8241-417F-924C-CE509AD30EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{6A097D4C-B92E-4D26-9D5E-6E9B3CB10636}"/>
   </bookViews>
@@ -2730,28 +2730,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-426.70650000000001</c:v>
+                  <c:v>2.403</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-912.85230000000001</c:v>
+                  <c:v>2.1688999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1323.2026000000001</c:v>
+                  <c:v>1.9721</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1705.69</c:v>
+                  <c:v>1.7967</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1956.3345999999999</c:v>
+                  <c:v>1.6339999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2176.2683999999999</c:v>
+                  <c:v>1.5041</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2399.0408000000002</c:v>
+                  <c:v>1.3963000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2475.1684</c:v>
+                  <c:v>1.2485999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16074,7 +16074,7 @@
         <v>52.535570059999998</v>
       </c>
       <c r="D138" s="1">
-        <v>-426.70650000000001</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.45">
@@ -16085,7 +16085,7 @@
         <v>19.451226550000001</v>
       </c>
       <c r="D139" s="1">
-        <v>-912.85230000000001</v>
+        <v>2.1688999999999998</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.45">
@@ -16096,7 +16096,7 @@
         <v>13.28359435</v>
       </c>
       <c r="D140" s="1">
-        <v>-1323.2026000000001</v>
+        <v>1.9721</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.45">
@@ -16107,7 +16107,7 @@
         <v>9.4090917600000008</v>
       </c>
       <c r="D141" s="1">
-        <v>-1705.69</v>
+        <v>1.7967</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.45">
@@ -16118,7 +16118,7 @@
         <v>7.40901196</v>
       </c>
       <c r="D142" s="1">
-        <v>-1956.3345999999999</v>
+        <v>1.6339999999999999</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.45">
@@ -16129,7 +16129,7 @@
         <v>5.97244843</v>
       </c>
       <c r="D143" s="1">
-        <v>-2176.2683999999999</v>
+        <v>1.5041</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.45">
@@ -16140,7 +16140,7 @@
         <v>5.4243082600000001</v>
       </c>
       <c r="D144" s="1">
-        <v>-2399.0408000000002</v>
+        <v>1.3963000000000001</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.45">
@@ -16151,7 +16151,7 @@
         <v>4.6695108999999997</v>
       </c>
       <c r="D145" s="1">
-        <v>-2475.1684</v>
+        <v>1.2485999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/3DAG and 2D Tree/Data Summaries/Uniform 100 x 100.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/Uniform 100 x 100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CAB9C3-8241-417F-924C-CE509AD30EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AF2A8C-F6D0-40CC-9A47-277BA5C7346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{6A097D4C-B92E-4D26-9D5E-6E9B3CB10636}"/>
   </bookViews>
